--- a/Grid Database.xlsx
+++ b/Grid Database.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/a4bfe6e8f062496f/Desktop/Grid/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/a4bfe6e8f062496f/Desktop/Grid/GridApp/GridApp/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="176" documentId="8_{30167142-7360-4562-A86A-6E0411E62A9D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E37A855D-9F5D-41A0-9705-9C3E5702B867}"/>
+  <xr:revisionPtr revIDLastSave="178" documentId="8_{30167142-7360-4562-A86A-6E0411E62A9D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{90955AD4-9625-4FD6-A542-DDE96DE9B52B}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25180" windowHeight="16140" xr2:uid="{07F1D9CF-A2D1-42AB-8E4E-EAB3AA23EDEE}"/>
   </bookViews>
@@ -3774,13 +3774,13 @@
     </row>
     <row r="85" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A85">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B85" t="s">
-        <v>127</v>
+        <v>310</v>
       </c>
       <c r="C85" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D85" t="s">
         <v>118</v>
@@ -3789,38 +3789,38 @@
         <v>16</v>
       </c>
       <c r="F85">
-        <v>2018</v>
+        <v>2024</v>
       </c>
     </row>
     <row r="86" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A86">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B86" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="C86" t="s">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="D86" t="s">
-        <v>129</v>
+        <v>118</v>
       </c>
       <c r="E86" t="s">
         <v>16</v>
       </c>
       <c r="F86">
-        <v>2019</v>
+        <v>2018</v>
       </c>
     </row>
     <row r="87" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A87" t="s">
-        <v>27</v>
+      <c r="A87">
+        <v>2</v>
       </c>
       <c r="B87" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="C87" t="s">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="D87" t="s">
         <v>129</v>
@@ -3829,18 +3829,18 @@
         <v>16</v>
       </c>
       <c r="F87">
-        <v>2020</v>
+        <v>2019</v>
       </c>
     </row>
     <row r="88" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A88">
-        <v>1</v>
+      <c r="A88" t="s">
+        <v>27</v>
       </c>
       <c r="B88" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="C88" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D88" t="s">
         <v>129</v>
@@ -3849,15 +3849,15 @@
         <v>16</v>
       </c>
       <c r="F88">
-        <v>2016</v>
+        <v>2020</v>
       </c>
     </row>
     <row r="89" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A89">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B89" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="C89" t="s">
         <v>13</v>
@@ -3869,7 +3869,7 @@
         <v>16</v>
       </c>
       <c r="F89">
-        <v>2013</v>
+        <v>2016</v>
       </c>
     </row>
     <row r="90" spans="1:6" x14ac:dyDescent="0.35">
@@ -3877,7 +3877,7 @@
         <v>2</v>
       </c>
       <c r="B90" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="C90" t="s">
         <v>13</v>
@@ -3889,15 +3889,15 @@
         <v>16</v>
       </c>
       <c r="F90">
-        <v>2023</v>
+        <v>2013</v>
       </c>
     </row>
     <row r="91" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A91" t="s">
-        <v>54</v>
+      <c r="A91">
+        <v>2</v>
       </c>
       <c r="B91" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="C91" t="s">
         <v>13</v>
@@ -3909,18 +3909,18 @@
         <v>16</v>
       </c>
       <c r="F91">
-        <v>2022</v>
+        <v>2023</v>
       </c>
     </row>
     <row r="92" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A92" t="s">
-        <v>27</v>
+        <v>54</v>
       </c>
       <c r="B92" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="C92" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D92" t="s">
         <v>129</v>
@@ -3929,7 +3929,7 @@
         <v>16</v>
       </c>
       <c r="F92">
-        <v>2025</v>
+        <v>2022</v>
       </c>
     </row>
     <row r="93" spans="1:6" x14ac:dyDescent="0.35">
@@ -3937,30 +3937,30 @@
         <v>27</v>
       </c>
       <c r="B93" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="C93" t="s">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="D93" t="s">
-        <v>137</v>
+        <v>129</v>
       </c>
       <c r="E93" t="s">
         <v>16</v>
       </c>
       <c r="F93">
-        <v>2021</v>
+        <v>2025</v>
       </c>
     </row>
     <row r="94" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A94">
-        <v>2</v>
+      <c r="A94" t="s">
+        <v>27</v>
       </c>
       <c r="B94" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="C94" t="s">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="D94" t="s">
         <v>137</v>
@@ -3969,7 +3969,7 @@
         <v>16</v>
       </c>
       <c r="F94">
-        <v>2025</v>
+        <v>2021</v>
       </c>
     </row>
     <row r="95" spans="1:6" x14ac:dyDescent="0.35">
@@ -3977,7 +3977,7 @@
         <v>2</v>
       </c>
       <c r="B95" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="C95" t="s">
         <v>12</v>
@@ -3989,15 +3989,15 @@
         <v>16</v>
       </c>
       <c r="F95">
-        <v>2023</v>
+        <v>2025</v>
       </c>
     </row>
     <row r="96" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A96">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B96" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="C96" t="s">
         <v>12</v>
@@ -4009,18 +4009,18 @@
         <v>16</v>
       </c>
       <c r="F96">
-        <v>2025</v>
+        <v>2023</v>
       </c>
     </row>
     <row r="97" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A97">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B97" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="C97" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D97" t="s">
         <v>137</v>
@@ -4029,7 +4029,7 @@
         <v>16</v>
       </c>
       <c r="F97">
-        <v>2024</v>
+        <v>2025</v>
       </c>
     </row>
     <row r="98" spans="1:6" x14ac:dyDescent="0.35">
@@ -4037,7 +4037,7 @@
         <v>2</v>
       </c>
       <c r="B98" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="C98" t="s">
         <v>13</v>
@@ -4049,15 +4049,15 @@
         <v>16</v>
       </c>
       <c r="F98">
-        <v>2019</v>
+        <v>2024</v>
       </c>
     </row>
     <row r="99" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A99" t="s">
-        <v>54</v>
+      <c r="A99">
+        <v>2</v>
       </c>
       <c r="B99" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="C99" t="s">
         <v>13</v>
@@ -4069,15 +4069,15 @@
         <v>16</v>
       </c>
       <c r="F99">
-        <v>2023</v>
+        <v>2019</v>
       </c>
     </row>
     <row r="100" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A100">
-        <v>1</v>
+      <c r="A100" t="s">
+        <v>54</v>
       </c>
       <c r="B100" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="C100" t="s">
         <v>13</v>
@@ -4089,15 +4089,15 @@
         <v>16</v>
       </c>
       <c r="F100">
-        <v>2026</v>
+        <v>2023</v>
       </c>
     </row>
     <row r="101" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A101">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B101" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="C101" t="s">
         <v>13</v>
@@ -4109,7 +4109,7 @@
         <v>16</v>
       </c>
       <c r="F101">
-        <v>2025</v>
+        <v>2026</v>
       </c>
     </row>
     <row r="102" spans="1:6" x14ac:dyDescent="0.35">
@@ -4117,10 +4117,10 @@
         <v>2</v>
       </c>
       <c r="B102" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="C102" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D102" t="s">
         <v>137</v>
@@ -4129,15 +4129,15 @@
         <v>16</v>
       </c>
       <c r="F102">
-        <v>2023</v>
+        <v>2025</v>
       </c>
     </row>
     <row r="103" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A103">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B103" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="C103" t="s">
         <v>14</v>
@@ -4149,7 +4149,7 @@
         <v>16</v>
       </c>
       <c r="F103">
-        <v>2026</v>
+        <v>2023</v>
       </c>
     </row>
     <row r="104" spans="1:6" x14ac:dyDescent="0.35">
@@ -4157,30 +4157,30 @@
         <v>1</v>
       </c>
       <c r="B104" t="s">
-        <v>42</v>
+        <v>147</v>
       </c>
       <c r="C104" t="s">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="D104" t="s">
-        <v>15</v>
+        <v>137</v>
       </c>
       <c r="E104" t="s">
         <v>16</v>
       </c>
       <c r="F104">
-        <v>2025</v>
+        <v>2026</v>
       </c>
     </row>
     <row r="105" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A105">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B105" t="s">
-        <v>148</v>
+        <v>42</v>
       </c>
       <c r="C105" t="s">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="D105" t="s">
         <v>15</v>
@@ -4189,7 +4189,7 @@
         <v>16</v>
       </c>
       <c r="F105">
-        <v>2019</v>
+        <v>2025</v>
       </c>
     </row>
     <row r="106" spans="1:6" x14ac:dyDescent="0.35">
@@ -4197,7 +4197,7 @@
         <v>2</v>
       </c>
       <c r="B106" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="C106" t="s">
         <v>12</v>
@@ -4209,15 +4209,15 @@
         <v>16</v>
       </c>
       <c r="F106">
-        <v>2023</v>
+        <v>2019</v>
       </c>
     </row>
     <row r="107" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A107">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B107" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="C107" t="s">
         <v>12</v>
@@ -4229,7 +4229,7 @@
         <v>16</v>
       </c>
       <c r="F107">
-        <v>2026</v>
+        <v>2023</v>
       </c>
     </row>
     <row r="108" spans="1:6" x14ac:dyDescent="0.35">
@@ -4237,10 +4237,10 @@
         <v>1</v>
       </c>
       <c r="B108" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="C108" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D108" t="s">
         <v>15</v>
@@ -4249,15 +4249,15 @@
         <v>16</v>
       </c>
       <c r="F108">
-        <v>2025</v>
+        <v>2026</v>
       </c>
     </row>
     <row r="109" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A109" t="s">
-        <v>54</v>
+      <c r="A109">
+        <v>1</v>
       </c>
       <c r="B109" t="s">
-        <v>48</v>
+        <v>151</v>
       </c>
       <c r="C109" t="s">
         <v>13</v>
@@ -4269,15 +4269,15 @@
         <v>16</v>
       </c>
       <c r="F109">
-        <v>2026</v>
+        <v>2025</v>
       </c>
     </row>
     <row r="110" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A110">
-        <v>2</v>
+      <c r="A110" t="s">
+        <v>54</v>
       </c>
       <c r="B110" t="s">
-        <v>152</v>
+        <v>48</v>
       </c>
       <c r="C110" t="s">
         <v>13</v>
@@ -4289,7 +4289,7 @@
         <v>16</v>
       </c>
       <c r="F110">
-        <v>2022</v>
+        <v>2026</v>
       </c>
     </row>
     <row r="111" spans="1:6" x14ac:dyDescent="0.35">
@@ -4297,7 +4297,7 @@
         <v>2</v>
       </c>
       <c r="B111" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="C111" t="s">
         <v>13</v>
@@ -4309,15 +4309,15 @@
         <v>16</v>
       </c>
       <c r="F111">
-        <v>2018</v>
+        <v>2022</v>
       </c>
     </row>
     <row r="112" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A112">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B112" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="C112" t="s">
         <v>13</v>
@@ -4329,7 +4329,7 @@
         <v>16</v>
       </c>
       <c r="F112">
-        <v>2025</v>
+        <v>2018</v>
       </c>
     </row>
     <row r="113" spans="1:6" x14ac:dyDescent="0.35">
@@ -4337,10 +4337,10 @@
         <v>1</v>
       </c>
       <c r="B113" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="C113" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D113" t="s">
         <v>15</v>
@@ -4353,34 +4353,34 @@
       </c>
     </row>
     <row r="114" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A114" t="s">
+      <c r="A114">
+        <v>1</v>
+      </c>
+      <c r="B114" t="s">
+        <v>155</v>
+      </c>
+      <c r="C114" t="s">
+        <v>14</v>
+      </c>
+      <c r="D114" t="s">
+        <v>15</v>
+      </c>
+      <c r="E114" t="s">
+        <v>16</v>
+      </c>
+      <c r="F114">
+        <v>2025</v>
+      </c>
+    </row>
+    <row r="115" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A115" t="s">
         <v>54</v>
       </c>
-      <c r="B114" t="s">
+      <c r="B115" t="s">
         <v>156</v>
       </c>
-      <c r="C114" t="s">
+      <c r="C115" t="s">
         <v>7</v>
-      </c>
-      <c r="D114" t="s">
-        <v>157</v>
-      </c>
-      <c r="E114" t="s">
-        <v>158</v>
-      </c>
-      <c r="F114">
-        <v>2024</v>
-      </c>
-    </row>
-    <row r="115" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A115">
-        <v>2</v>
-      </c>
-      <c r="B115" t="s">
-        <v>159</v>
-      </c>
-      <c r="C115" t="s">
-        <v>12</v>
       </c>
       <c r="D115" t="s">
         <v>157</v>
@@ -4389,7 +4389,7 @@
         <v>158</v>
       </c>
       <c r="F115">
-        <v>2020</v>
+        <v>2024</v>
       </c>
     </row>
     <row r="116" spans="1:6" x14ac:dyDescent="0.35">
@@ -4397,7 +4397,7 @@
         <v>2</v>
       </c>
       <c r="B116" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="C116" t="s">
         <v>12</v>
@@ -4409,15 +4409,15 @@
         <v>158</v>
       </c>
       <c r="F116">
-        <v>2025</v>
+        <v>2020</v>
       </c>
     </row>
     <row r="117" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A117">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B117" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="C117" t="s">
         <v>12</v>
@@ -4429,18 +4429,18 @@
         <v>158</v>
       </c>
       <c r="F117">
-        <v>2026</v>
+        <v>2025</v>
       </c>
     </row>
     <row r="118" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A118" t="s">
-        <v>54</v>
+      <c r="A118">
+        <v>1</v>
       </c>
       <c r="B118" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="C118" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D118" t="s">
         <v>157</v>
@@ -4449,7 +4449,7 @@
         <v>158</v>
       </c>
       <c r="F118">
-        <v>2018</v>
+        <v>2026</v>
       </c>
     </row>
     <row r="119" spans="1:6" x14ac:dyDescent="0.35">
@@ -4457,7 +4457,7 @@
         <v>54</v>
       </c>
       <c r="B119" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="C119" t="s">
         <v>13</v>
@@ -4469,15 +4469,15 @@
         <v>158</v>
       </c>
       <c r="F119">
-        <v>2021</v>
+        <v>2018</v>
       </c>
     </row>
     <row r="120" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A120">
-        <v>1</v>
+      <c r="A120" t="s">
+        <v>54</v>
       </c>
       <c r="B120" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="C120" t="s">
         <v>13</v>
@@ -4489,7 +4489,7 @@
         <v>158</v>
       </c>
       <c r="F120">
-        <v>2024</v>
+        <v>2021</v>
       </c>
     </row>
     <row r="121" spans="1:6" x14ac:dyDescent="0.35">
@@ -4497,7 +4497,7 @@
         <v>1</v>
       </c>
       <c r="B121" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="C121" t="s">
         <v>13</v>
@@ -4509,18 +4509,18 @@
         <v>158</v>
       </c>
       <c r="F121">
-        <v>2023</v>
+        <v>2024</v>
       </c>
     </row>
     <row r="122" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A122">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B122" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="C122" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D122" t="s">
         <v>157</v>
@@ -4529,21 +4529,21 @@
         <v>158</v>
       </c>
       <c r="F122">
-        <v>2017</v>
+        <v>2023</v>
       </c>
     </row>
     <row r="123" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A123" t="s">
-        <v>27</v>
+      <c r="A123">
+        <v>2</v>
       </c>
       <c r="B123" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="C123" t="s">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="D123" t="s">
-        <v>168</v>
+        <v>157</v>
       </c>
       <c r="E123" t="s">
         <v>158</v>
@@ -4557,10 +4557,10 @@
         <v>27</v>
       </c>
       <c r="B124" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="C124" t="s">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="D124" t="s">
         <v>168</v>
@@ -4569,15 +4569,15 @@
         <v>158</v>
       </c>
       <c r="F124">
-        <v>2022</v>
+        <v>2017</v>
       </c>
     </row>
     <row r="125" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A125">
-        <v>1</v>
+      <c r="A125" t="s">
+        <v>27</v>
       </c>
       <c r="B125" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="C125" t="s">
         <v>12</v>
@@ -4589,7 +4589,7 @@
         <v>158</v>
       </c>
       <c r="F125">
-        <v>2026</v>
+        <v>2022</v>
       </c>
     </row>
     <row r="126" spans="1:6" x14ac:dyDescent="0.35">
@@ -4597,10 +4597,10 @@
         <v>1</v>
       </c>
       <c r="B126" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="C126" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D126" t="s">
         <v>168</v>
@@ -4609,15 +4609,15 @@
         <v>158</v>
       </c>
       <c r="F126">
-        <v>2022</v>
+        <v>2026</v>
       </c>
     </row>
     <row r="127" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A127">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B127" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="C127" t="s">
         <v>13</v>
@@ -4629,15 +4629,15 @@
         <v>158</v>
       </c>
       <c r="F127">
-        <v>2024</v>
+        <v>2022</v>
       </c>
     </row>
     <row r="128" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A128" t="s">
-        <v>54</v>
+      <c r="A128">
+        <v>2</v>
       </c>
       <c r="B128" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="C128" t="s">
         <v>13</v>
@@ -4649,18 +4649,18 @@
         <v>158</v>
       </c>
       <c r="F128">
-        <v>2023</v>
+        <v>2024</v>
       </c>
     </row>
     <row r="129" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A129" t="s">
-        <v>27</v>
+        <v>54</v>
       </c>
       <c r="B129" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="C129" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D129" t="s">
         <v>168</v>
@@ -4669,38 +4669,38 @@
         <v>158</v>
       </c>
       <c r="F129">
-        <v>2013</v>
+        <v>2023</v>
       </c>
     </row>
     <row r="130" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A130">
-        <v>2</v>
+      <c r="A130" t="s">
+        <v>27</v>
       </c>
       <c r="B130" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="C130" t="s">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="D130" t="s">
-        <v>176</v>
+        <v>168</v>
       </c>
       <c r="E130" t="s">
         <v>158</v>
       </c>
       <c r="F130">
-        <v>2012</v>
+        <v>2013</v>
       </c>
     </row>
     <row r="131" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A131" t="s">
-        <v>27</v>
+      <c r="A131">
+        <v>2</v>
       </c>
       <c r="B131" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="C131" t="s">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="D131" t="s">
         <v>176</v>
@@ -4709,15 +4709,15 @@
         <v>158</v>
       </c>
       <c r="F131">
-        <v>2025</v>
+        <v>2012</v>
       </c>
     </row>
     <row r="132" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A132">
-        <v>2</v>
+      <c r="A132" t="s">
+        <v>27</v>
       </c>
       <c r="B132" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="C132" t="s">
         <v>12</v>
@@ -4729,18 +4729,18 @@
         <v>158</v>
       </c>
       <c r="F132">
-        <v>2026</v>
+        <v>2025</v>
       </c>
     </row>
     <row r="133" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A133">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B133" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="C133" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D133" t="s">
         <v>176</v>
@@ -4749,7 +4749,7 @@
         <v>158</v>
       </c>
       <c r="F133">
-        <v>2022</v>
+        <v>2026</v>
       </c>
     </row>
     <row r="134" spans="1:6" x14ac:dyDescent="0.35">
@@ -4757,7 +4757,7 @@
         <v>1</v>
       </c>
       <c r="B134" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="C134" t="s">
         <v>13</v>
@@ -4769,15 +4769,15 @@
         <v>158</v>
       </c>
       <c r="F134">
-        <v>2020</v>
+        <v>2022</v>
       </c>
     </row>
     <row r="135" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A135">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B135" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="C135" t="s">
         <v>13</v>
@@ -4789,15 +4789,15 @@
         <v>158</v>
       </c>
       <c r="F135">
-        <v>2023</v>
+        <v>2020</v>
       </c>
     </row>
     <row r="136" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A136">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B136" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="C136" t="s">
         <v>13</v>
@@ -4809,18 +4809,18 @@
         <v>158</v>
       </c>
       <c r="F136">
-        <v>2025</v>
+        <v>2023</v>
       </c>
     </row>
     <row r="137" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A137" t="s">
-        <v>27</v>
+      <c r="A137">
+        <v>1</v>
       </c>
       <c r="B137" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="C137" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D137" t="s">
         <v>176</v>
@@ -4829,15 +4829,15 @@
         <v>158</v>
       </c>
       <c r="F137">
-        <v>2024</v>
+        <v>2025</v>
       </c>
     </row>
     <row r="138" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A138">
-        <v>2</v>
+      <c r="A138" t="s">
+        <v>27</v>
       </c>
       <c r="B138" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="C138" t="s">
         <v>14</v>
@@ -4849,7 +4849,7 @@
         <v>158</v>
       </c>
       <c r="F138">
-        <v>2023</v>
+        <v>2024</v>
       </c>
     </row>
     <row r="139" spans="1:6" x14ac:dyDescent="0.35">
@@ -4857,30 +4857,30 @@
         <v>2</v>
       </c>
       <c r="B139" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="C139" t="s">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="D139" t="s">
-        <v>186</v>
+        <v>176</v>
       </c>
       <c r="E139" t="s">
         <v>158</v>
       </c>
       <c r="F139">
-        <v>2020</v>
+        <v>2023</v>
       </c>
     </row>
     <row r="140" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A140" t="s">
-        <v>54</v>
+      <c r="A140">
+        <v>2</v>
       </c>
       <c r="B140" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="C140" t="s">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="D140" t="s">
         <v>186</v>
@@ -4889,15 +4889,15 @@
         <v>158</v>
       </c>
       <c r="F140">
-        <v>2025</v>
+        <v>2020</v>
       </c>
     </row>
     <row r="141" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A141">
-        <v>1</v>
+      <c r="A141" t="s">
+        <v>54</v>
       </c>
       <c r="B141" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="C141" t="s">
         <v>12</v>
@@ -4909,18 +4909,18 @@
         <v>158</v>
       </c>
       <c r="F141">
-        <v>2023</v>
+        <v>2025</v>
       </c>
     </row>
     <row r="142" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A142">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B142" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="C142" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D142" t="s">
         <v>186</v>
@@ -4937,7 +4937,7 @@
         <v>2</v>
       </c>
       <c r="B143" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="C143" t="s">
         <v>13</v>
@@ -4949,15 +4949,15 @@
         <v>158</v>
       </c>
       <c r="F143">
-        <v>2025</v>
+        <v>2023</v>
       </c>
     </row>
     <row r="144" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A144" t="s">
-        <v>54</v>
+      <c r="A144">
+        <v>2</v>
       </c>
       <c r="B144" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="C144" t="s">
         <v>13</v>
@@ -4969,18 +4969,18 @@
         <v>158</v>
       </c>
       <c r="F144">
-        <v>2024</v>
+        <v>2025</v>
       </c>
     </row>
     <row r="145" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A145">
-        <v>2</v>
+      <c r="A145" t="s">
+        <v>54</v>
       </c>
       <c r="B145" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="C145" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D145" t="s">
         <v>186</v>
@@ -4989,15 +4989,15 @@
         <v>158</v>
       </c>
       <c r="F145">
-        <v>2017</v>
+        <v>2024</v>
       </c>
     </row>
     <row r="146" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A146">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B146" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="C146" t="s">
         <v>14</v>
@@ -5009,7 +5009,7 @@
         <v>158</v>
       </c>
       <c r="F146">
-        <v>2022</v>
+        <v>2017</v>
       </c>
     </row>
     <row r="147" spans="1:6" x14ac:dyDescent="0.35">
@@ -5017,7 +5017,7 @@
         <v>1</v>
       </c>
       <c r="B147" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="C147" t="s">
         <v>14</v>
@@ -5029,27 +5029,27 @@
         <v>158</v>
       </c>
       <c r="F147">
+        <v>2022</v>
+      </c>
+    </row>
+    <row r="148" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A148">
+        <v>1</v>
+      </c>
+      <c r="B148" t="s">
+        <v>194</v>
+      </c>
+      <c r="C148" t="s">
+        <v>14</v>
+      </c>
+      <c r="D148" t="s">
+        <v>186</v>
+      </c>
+      <c r="E148" t="s">
+        <v>158</v>
+      </c>
+      <c r="F148">
         <v>2025</v>
-      </c>
-    </row>
-    <row r="148" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A148" t="s">
-        <v>54</v>
-      </c>
-      <c r="B148" t="s">
-        <v>195</v>
-      </c>
-      <c r="C148" t="s">
-        <v>7</v>
-      </c>
-      <c r="D148" t="s">
-        <v>196</v>
-      </c>
-      <c r="E148" t="s">
-        <v>197</v>
-      </c>
-      <c r="F148">
-        <v>2016</v>
       </c>
     </row>
     <row r="149" spans="1:6" x14ac:dyDescent="0.35">
@@ -5057,10 +5057,10 @@
         <v>54</v>
       </c>
       <c r="B149" t="s">
-        <v>198</v>
+        <v>195</v>
       </c>
       <c r="C149" t="s">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="D149" t="s">
         <v>196</v>
@@ -5069,18 +5069,18 @@
         <v>197</v>
       </c>
       <c r="F149">
-        <v>2021</v>
+        <v>2016</v>
       </c>
     </row>
     <row r="150" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A150" t="s">
-        <v>27</v>
+        <v>54</v>
       </c>
       <c r="B150" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="C150" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D150" t="s">
         <v>196</v>
@@ -5089,7 +5089,7 @@
         <v>197</v>
       </c>
       <c r="F150">
-        <v>2022</v>
+        <v>2021</v>
       </c>
     </row>
     <row r="151" spans="1:6" x14ac:dyDescent="0.35">
@@ -5097,7 +5097,7 @@
         <v>27</v>
       </c>
       <c r="B151" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="C151" t="s">
         <v>13</v>
@@ -5109,15 +5109,15 @@
         <v>197</v>
       </c>
       <c r="F151">
-        <v>2020</v>
+        <v>2022</v>
       </c>
     </row>
     <row r="152" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A152">
-        <v>1</v>
+      <c r="A152" t="s">
+        <v>27</v>
       </c>
       <c r="B152" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="C152" t="s">
         <v>13</v>
@@ -5129,7 +5129,7 @@
         <v>197</v>
       </c>
       <c r="F152">
-        <v>2024</v>
+        <v>2020</v>
       </c>
     </row>
     <row r="153" spans="1:6" x14ac:dyDescent="0.35">
@@ -5137,7 +5137,7 @@
         <v>1</v>
       </c>
       <c r="B153" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="C153" t="s">
         <v>13</v>
@@ -5149,18 +5149,18 @@
         <v>197</v>
       </c>
       <c r="F153">
-        <v>2019</v>
+        <v>2024</v>
       </c>
     </row>
     <row r="154" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A154" t="s">
-        <v>54</v>
+      <c r="A154">
+        <v>1</v>
       </c>
       <c r="B154" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="C154" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D154" t="s">
         <v>196</v>
@@ -5169,38 +5169,38 @@
         <v>197</v>
       </c>
       <c r="F154">
-        <v>2022</v>
+        <v>2019</v>
       </c>
     </row>
     <row r="155" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A155">
-        <v>1</v>
+      <c r="A155" t="s">
+        <v>54</v>
       </c>
       <c r="B155" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="C155" t="s">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="D155" t="s">
-        <v>205</v>
+        <v>196</v>
       </c>
       <c r="E155" t="s">
         <v>197</v>
       </c>
       <c r="F155">
-        <v>2015</v>
+        <v>2022</v>
       </c>
     </row>
     <row r="156" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A156" t="s">
-        <v>54</v>
+      <c r="A156">
+        <v>1</v>
       </c>
       <c r="B156" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="C156" t="s">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="D156" t="s">
         <v>205</v>
@@ -5209,15 +5209,15 @@
         <v>197</v>
       </c>
       <c r="F156">
-        <v>2025</v>
+        <v>2015</v>
       </c>
     </row>
     <row r="157" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A157">
-        <v>1</v>
+      <c r="A157" t="s">
+        <v>54</v>
       </c>
       <c r="B157" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="C157" t="s">
         <v>12</v>
@@ -5229,7 +5229,7 @@
         <v>197</v>
       </c>
       <c r="F157">
-        <v>2021</v>
+        <v>2025</v>
       </c>
     </row>
     <row r="158" spans="1:6" x14ac:dyDescent="0.35">
@@ -5237,7 +5237,7 @@
         <v>1</v>
       </c>
       <c r="B158" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="C158" t="s">
         <v>12</v>
@@ -5249,7 +5249,7 @@
         <v>197</v>
       </c>
       <c r="F158">
-        <v>2024</v>
+        <v>2021</v>
       </c>
     </row>
     <row r="159" spans="1:6" x14ac:dyDescent="0.35">
@@ -5257,7 +5257,7 @@
         <v>1</v>
       </c>
       <c r="B159" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="C159" t="s">
         <v>12</v>
@@ -5269,18 +5269,18 @@
         <v>197</v>
       </c>
       <c r="F159">
-        <v>2019</v>
+        <v>2024</v>
       </c>
     </row>
     <row r="160" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A160" t="s">
-        <v>27</v>
+      <c r="A160">
+        <v>1</v>
       </c>
       <c r="B160" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="C160" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D160" t="s">
         <v>205</v>
@@ -5289,15 +5289,15 @@
         <v>197</v>
       </c>
       <c r="F160">
-        <v>2024</v>
+        <v>2019</v>
       </c>
     </row>
     <row r="161" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A161">
-        <v>1</v>
+      <c r="A161" t="s">
+        <v>27</v>
       </c>
       <c r="B161" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="C161" t="s">
         <v>13</v>
@@ -5309,7 +5309,7 @@
         <v>197</v>
       </c>
       <c r="F161">
-        <v>2026</v>
+        <v>2024</v>
       </c>
     </row>
     <row r="162" spans="1:6" x14ac:dyDescent="0.35">
@@ -5317,7 +5317,7 @@
         <v>1</v>
       </c>
       <c r="B162" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="C162" t="s">
         <v>13</v>
@@ -5329,18 +5329,18 @@
         <v>197</v>
       </c>
       <c r="F162">
-        <v>2020</v>
+        <v>2026</v>
       </c>
     </row>
     <row r="163" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A163">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B163" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="C163" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D163" t="s">
         <v>205</v>
@@ -5349,15 +5349,15 @@
         <v>197</v>
       </c>
       <c r="F163">
-        <v>2022</v>
+        <v>2020</v>
       </c>
     </row>
     <row r="164" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A164">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B164" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="C164" t="s">
         <v>14</v>
@@ -5369,38 +5369,38 @@
         <v>197</v>
       </c>
       <c r="F164">
-        <v>2024</v>
+        <v>2022</v>
       </c>
     </row>
     <row r="165" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A165" t="s">
-        <v>54</v>
+      <c r="A165">
+        <v>1</v>
       </c>
       <c r="B165" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="C165" t="s">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="D165" t="s">
-        <v>216</v>
+        <v>205</v>
       </c>
       <c r="E165" t="s">
         <v>197</v>
       </c>
       <c r="F165">
-        <v>2020</v>
+        <v>2024</v>
       </c>
     </row>
     <row r="166" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A166" t="s">
-        <v>27</v>
+        <v>54</v>
       </c>
       <c r="B166" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="C166" t="s">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="D166" t="s">
         <v>216</v>
@@ -5409,15 +5409,15 @@
         <v>197</v>
       </c>
       <c r="F166">
-        <v>2018</v>
+        <v>2020</v>
       </c>
     </row>
     <row r="167" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A167">
-        <v>1</v>
+      <c r="A167" t="s">
+        <v>27</v>
       </c>
       <c r="B167" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="C167" t="s">
         <v>12</v>
@@ -5429,18 +5429,18 @@
         <v>197</v>
       </c>
       <c r="F167">
-        <v>2024</v>
+        <v>2018</v>
       </c>
     </row>
     <row r="168" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A168">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B168" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="C168" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D168" t="s">
         <v>216</v>
@@ -5449,15 +5449,15 @@
         <v>197</v>
       </c>
       <c r="F168">
-        <v>2023</v>
+        <v>2024</v>
       </c>
     </row>
     <row r="169" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A169" t="s">
-        <v>27</v>
+      <c r="A169">
+        <v>2</v>
       </c>
       <c r="B169" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="C169" t="s">
         <v>13</v>
@@ -5469,15 +5469,15 @@
         <v>197</v>
       </c>
       <c r="F169">
-        <v>2021</v>
+        <v>2023</v>
       </c>
     </row>
     <row r="170" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A170">
-        <v>2</v>
+      <c r="A170" t="s">
+        <v>27</v>
       </c>
       <c r="B170" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="C170" t="s">
         <v>13</v>
@@ -5489,15 +5489,15 @@
         <v>197</v>
       </c>
       <c r="F170">
-        <v>2026</v>
+        <v>2021</v>
       </c>
     </row>
     <row r="171" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A171">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B171" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="C171" t="s">
         <v>13</v>
@@ -5509,7 +5509,7 @@
         <v>197</v>
       </c>
       <c r="F171">
-        <v>2019</v>
+        <v>2026</v>
       </c>
     </row>
     <row r="172" spans="1:6" x14ac:dyDescent="0.35">
@@ -5517,7 +5517,7 @@
         <v>1</v>
       </c>
       <c r="B172" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="C172" t="s">
         <v>13</v>
@@ -5529,18 +5529,18 @@
         <v>197</v>
       </c>
       <c r="F172">
-        <v>2025</v>
+        <v>2019</v>
       </c>
     </row>
     <row r="173" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A173" t="s">
-        <v>54</v>
+      <c r="A173">
+        <v>1</v>
       </c>
       <c r="B173" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="C173" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D173" t="s">
         <v>216</v>
@@ -5549,7 +5549,7 @@
         <v>197</v>
       </c>
       <c r="F173">
-        <v>2018</v>
+        <v>2025</v>
       </c>
     </row>
     <row r="174" spans="1:6" x14ac:dyDescent="0.35">
@@ -5557,30 +5557,30 @@
         <v>54</v>
       </c>
       <c r="B174" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="C174" t="s">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="D174" t="s">
-        <v>226</v>
+        <v>216</v>
       </c>
       <c r="E174" t="s">
         <v>197</v>
       </c>
       <c r="F174">
-        <v>2024</v>
+        <v>2018</v>
       </c>
     </row>
     <row r="175" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A175">
-        <v>2</v>
+      <c r="A175" t="s">
+        <v>54</v>
       </c>
       <c r="B175" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="C175" t="s">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="D175" t="s">
         <v>226</v>
@@ -5589,7 +5589,7 @@
         <v>197</v>
       </c>
       <c r="F175">
-        <v>2025</v>
+        <v>2024</v>
       </c>
     </row>
     <row r="176" spans="1:6" x14ac:dyDescent="0.35">
@@ -5597,7 +5597,7 @@
         <v>2</v>
       </c>
       <c r="B176" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="C176" t="s">
         <v>12</v>
@@ -5609,15 +5609,15 @@
         <v>197</v>
       </c>
       <c r="F176">
-        <v>2022</v>
+        <v>2025</v>
       </c>
     </row>
     <row r="177" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A177">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B177" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="C177" t="s">
         <v>12</v>
@@ -5629,18 +5629,18 @@
         <v>197</v>
       </c>
       <c r="F177">
-        <v>2017</v>
+        <v>2022</v>
       </c>
     </row>
     <row r="178" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A178" t="s">
-        <v>54</v>
+      <c r="A178">
+        <v>1</v>
       </c>
       <c r="B178" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="C178" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D178" t="s">
         <v>226</v>
@@ -5649,7 +5649,7 @@
         <v>197</v>
       </c>
       <c r="F178">
-        <v>2019</v>
+        <v>2017</v>
       </c>
     </row>
     <row r="179" spans="1:6" x14ac:dyDescent="0.35">
@@ -5657,7 +5657,7 @@
         <v>54</v>
       </c>
       <c r="B179" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="C179" t="s">
         <v>13</v>
@@ -5669,15 +5669,15 @@
         <v>197</v>
       </c>
       <c r="F179">
-        <v>2015</v>
+        <v>2019</v>
       </c>
     </row>
     <row r="180" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A180">
-        <v>1</v>
+      <c r="A180" t="s">
+        <v>54</v>
       </c>
       <c r="B180" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="C180" t="s">
         <v>13</v>
@@ -5689,18 +5689,18 @@
         <v>197</v>
       </c>
       <c r="F180">
-        <v>2026</v>
+        <v>2015</v>
       </c>
     </row>
     <row r="181" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A181">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B181" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="C181" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D181" t="s">
         <v>226</v>
@@ -5709,27 +5709,27 @@
         <v>197</v>
       </c>
       <c r="F181">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="182" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A182">
+        <v>2</v>
+      </c>
+      <c r="B182" t="s">
+        <v>233</v>
+      </c>
+      <c r="C182" t="s">
+        <v>14</v>
+      </c>
+      <c r="D182" t="s">
+        <v>226</v>
+      </c>
+      <c r="E182" t="s">
+        <v>197</v>
+      </c>
+      <c r="F182">
         <v>2022</v>
-      </c>
-    </row>
-    <row r="182" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A182" t="s">
-        <v>54</v>
-      </c>
-      <c r="B182" t="s">
-        <v>234</v>
-      </c>
-      <c r="C182" t="s">
-        <v>7</v>
-      </c>
-      <c r="D182" t="s">
-        <v>17</v>
-      </c>
-      <c r="E182" t="s">
-        <v>18</v>
-      </c>
-      <c r="F182">
-        <v>2024</v>
       </c>
     </row>
     <row r="183" spans="1:6" x14ac:dyDescent="0.35">
@@ -5737,10 +5737,10 @@
         <v>54</v>
       </c>
       <c r="B183" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="C183" t="s">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="D183" t="s">
         <v>17</v>
@@ -5749,15 +5749,15 @@
         <v>18</v>
       </c>
       <c r="F183">
-        <v>2020</v>
+        <v>2024</v>
       </c>
     </row>
     <row r="184" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A184">
-        <v>2</v>
+      <c r="A184" t="s">
+        <v>54</v>
       </c>
       <c r="B184" t="s">
-        <v>46</v>
+        <v>235</v>
       </c>
       <c r="C184" t="s">
         <v>12</v>
@@ -5769,15 +5769,15 @@
         <v>18</v>
       </c>
       <c r="F184">
-        <v>2025</v>
+        <v>2020</v>
       </c>
     </row>
     <row r="185" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A185">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B185" t="s">
-        <v>236</v>
+        <v>46</v>
       </c>
       <c r="C185" t="s">
         <v>12</v>
@@ -5789,18 +5789,18 @@
         <v>18</v>
       </c>
       <c r="F185">
-        <v>2023</v>
+        <v>2025</v>
       </c>
     </row>
     <row r="186" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A186" t="s">
-        <v>54</v>
+      <c r="A186">
+        <v>1</v>
       </c>
       <c r="B186" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="C186" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D186" t="s">
         <v>17</v>
@@ -5809,7 +5809,7 @@
         <v>18</v>
       </c>
       <c r="F186">
-        <v>2024</v>
+        <v>2023</v>
       </c>
     </row>
     <row r="187" spans="1:6" x14ac:dyDescent="0.35">
@@ -5817,7 +5817,7 @@
         <v>54</v>
       </c>
       <c r="B187" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="C187" t="s">
         <v>13</v>
@@ -5829,15 +5829,15 @@
         <v>18</v>
       </c>
       <c r="F187">
-        <v>2025</v>
+        <v>2024</v>
       </c>
     </row>
     <row r="188" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A188">
-        <v>2</v>
+      <c r="A188" t="s">
+        <v>54</v>
       </c>
       <c r="B188" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="C188" t="s">
         <v>13</v>
@@ -5849,15 +5849,15 @@
         <v>18</v>
       </c>
       <c r="F188">
-        <v>2016</v>
+        <v>2025</v>
       </c>
     </row>
     <row r="189" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A189">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B189" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="C189" t="s">
         <v>13</v>
@@ -5869,7 +5869,7 @@
         <v>18</v>
       </c>
       <c r="F189">
-        <v>2025</v>
+        <v>2016</v>
       </c>
     </row>
     <row r="190" spans="1:6" x14ac:dyDescent="0.35">
@@ -5877,7 +5877,7 @@
         <v>1</v>
       </c>
       <c r="B190" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="C190" t="s">
         <v>13</v>
@@ -5889,18 +5889,18 @@
         <v>18</v>
       </c>
       <c r="F190">
-        <v>2026</v>
+        <v>2025</v>
       </c>
     </row>
     <row r="191" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A191" t="s">
-        <v>54</v>
+      <c r="A191">
+        <v>1</v>
       </c>
       <c r="B191" t="s">
-        <v>43</v>
+        <v>241</v>
       </c>
       <c r="C191" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D191" t="s">
         <v>17</v>
@@ -5909,15 +5909,15 @@
         <v>18</v>
       </c>
       <c r="F191">
-        <v>2025</v>
+        <v>2026</v>
       </c>
     </row>
     <row r="192" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A192">
-        <v>2</v>
+      <c r="A192" t="s">
+        <v>54</v>
       </c>
       <c r="B192" t="s">
-        <v>242</v>
+        <v>43</v>
       </c>
       <c r="C192" t="s">
         <v>14</v>
@@ -5929,38 +5929,38 @@
         <v>18</v>
       </c>
       <c r="F192">
-        <v>2020</v>
+        <v>2025</v>
       </c>
     </row>
     <row r="193" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A193" t="s">
-        <v>54</v>
+      <c r="A193">
+        <v>2</v>
       </c>
       <c r="B193" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="C193" t="s">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="D193" t="s">
-        <v>244</v>
+        <v>17</v>
       </c>
       <c r="E193" t="s">
         <v>18</v>
       </c>
       <c r="F193">
-        <v>2016</v>
+        <v>2020</v>
       </c>
     </row>
     <row r="194" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A194" t="s">
-        <v>27</v>
+        <v>54</v>
       </c>
       <c r="B194" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="C194" t="s">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="D194" t="s">
         <v>244</v>
@@ -5969,18 +5969,18 @@
         <v>18</v>
       </c>
       <c r="F194">
-        <v>2023</v>
+        <v>2016</v>
       </c>
     </row>
     <row r="195" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A195">
-        <v>1</v>
+      <c r="A195" t="s">
+        <v>27</v>
       </c>
       <c r="B195" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="C195" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D195" t="s">
         <v>244</v>
@@ -5989,15 +5989,15 @@
         <v>18</v>
       </c>
       <c r="F195">
-        <v>2025</v>
+        <v>2023</v>
       </c>
     </row>
     <row r="196" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A196" t="s">
-        <v>27</v>
+      <c r="A196">
+        <v>1</v>
       </c>
       <c r="B196" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="C196" t="s">
         <v>13</v>
@@ -6009,15 +6009,15 @@
         <v>18</v>
       </c>
       <c r="F196">
-        <v>2021</v>
+        <v>2025</v>
       </c>
     </row>
     <row r="197" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A197" t="s">
-        <v>54</v>
+        <v>27</v>
       </c>
       <c r="B197" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="C197" t="s">
         <v>13</v>
@@ -6029,7 +6029,7 @@
         <v>18</v>
       </c>
       <c r="F197">
-        <v>2022</v>
+        <v>2021</v>
       </c>
     </row>
     <row r="198" spans="1:6" x14ac:dyDescent="0.35">
@@ -6037,10 +6037,10 @@
         <v>54</v>
       </c>
       <c r="B198" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="C198" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D198" t="s">
         <v>244</v>
@@ -6049,38 +6049,38 @@
         <v>18</v>
       </c>
       <c r="F198">
-        <v>2023</v>
+        <v>2022</v>
       </c>
     </row>
     <row r="199" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A199">
-        <v>2</v>
+      <c r="A199" t="s">
+        <v>54</v>
       </c>
       <c r="B199" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="C199" t="s">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="D199" t="s">
-        <v>251</v>
+        <v>244</v>
       </c>
       <c r="E199" t="s">
         <v>18</v>
       </c>
       <c r="F199">
-        <v>2020</v>
+        <v>2023</v>
       </c>
     </row>
     <row r="200" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A200">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B200" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="C200" t="s">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="D200" t="s">
         <v>251</v>
@@ -6089,7 +6089,7 @@
         <v>18</v>
       </c>
       <c r="F200">
-        <v>2024</v>
+        <v>2020</v>
       </c>
     </row>
     <row r="201" spans="1:6" x14ac:dyDescent="0.35">
@@ -6097,7 +6097,7 @@
         <v>1</v>
       </c>
       <c r="B201" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="C201" t="s">
         <v>12</v>
@@ -6109,7 +6109,7 @@
         <v>18</v>
       </c>
       <c r="F201">
-        <v>2025</v>
+        <v>2024</v>
       </c>
     </row>
     <row r="202" spans="1:6" x14ac:dyDescent="0.35">
@@ -6117,7 +6117,7 @@
         <v>1</v>
       </c>
       <c r="B202" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="C202" t="s">
         <v>12</v>
@@ -6129,18 +6129,18 @@
         <v>18</v>
       </c>
       <c r="F202">
-        <v>2023</v>
+        <v>2025</v>
       </c>
     </row>
     <row r="203" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A203" t="s">
-        <v>54</v>
+      <c r="A203">
+        <v>1</v>
       </c>
       <c r="B203" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="C203" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D203" t="s">
         <v>251</v>
@@ -6149,7 +6149,7 @@
         <v>18</v>
       </c>
       <c r="F203">
-        <v>2022</v>
+        <v>2023</v>
       </c>
     </row>
     <row r="204" spans="1:6" x14ac:dyDescent="0.35">
@@ -6157,7 +6157,7 @@
         <v>54</v>
       </c>
       <c r="B204" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="C204" t="s">
         <v>13</v>
@@ -6169,15 +6169,15 @@
         <v>18</v>
       </c>
       <c r="F204">
-        <v>2025</v>
+        <v>2022</v>
       </c>
     </row>
     <row r="205" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A205">
-        <v>1</v>
+      <c r="A205" t="s">
+        <v>54</v>
       </c>
       <c r="B205" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="C205" t="s">
         <v>13</v>
@@ -6189,18 +6189,18 @@
         <v>18</v>
       </c>
       <c r="F205">
-        <v>2022</v>
+        <v>2025</v>
       </c>
     </row>
     <row r="206" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A206" t="s">
-        <v>54</v>
+      <c r="A206">
+        <v>1</v>
       </c>
       <c r="B206" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="C206" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D206" t="s">
         <v>251</v>
@@ -6209,15 +6209,15 @@
         <v>18</v>
       </c>
       <c r="F206">
-        <v>2023</v>
+        <v>2022</v>
       </c>
     </row>
     <row r="207" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A207">
-        <v>2</v>
+      <c r="A207" t="s">
+        <v>54</v>
       </c>
       <c r="B207" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="C207" t="s">
         <v>14</v>
@@ -6229,7 +6229,7 @@
         <v>18</v>
       </c>
       <c r="F207">
-        <v>2017</v>
+        <v>2023</v>
       </c>
     </row>
     <row r="208" spans="1:6" x14ac:dyDescent="0.35">
@@ -6237,30 +6237,30 @@
         <v>2</v>
       </c>
       <c r="B208" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="C208" t="s">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="D208" t="s">
-        <v>261</v>
+        <v>251</v>
       </c>
       <c r="E208" t="s">
         <v>18</v>
       </c>
       <c r="F208">
-        <v>2019</v>
+        <v>2017</v>
       </c>
     </row>
     <row r="209" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A209" t="s">
-        <v>54</v>
+      <c r="A209">
+        <v>2</v>
       </c>
       <c r="B209" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="C209" t="s">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="D209" t="s">
         <v>261</v>
@@ -6269,18 +6269,18 @@
         <v>18</v>
       </c>
       <c r="F209">
-        <v>2017</v>
+        <v>2019</v>
       </c>
     </row>
     <row r="210" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A210" t="s">
-        <v>27</v>
+        <v>54</v>
       </c>
       <c r="B210" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="C210" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D210" t="s">
         <v>261</v>
@@ -6289,15 +6289,15 @@
         <v>18</v>
       </c>
       <c r="F210">
-        <v>2020</v>
+        <v>2017</v>
       </c>
     </row>
     <row r="211" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A211">
-        <v>2</v>
+      <c r="A211" t="s">
+        <v>27</v>
       </c>
       <c r="B211" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="C211" t="s">
         <v>13</v>
@@ -6309,15 +6309,15 @@
         <v>18</v>
       </c>
       <c r="F211">
-        <v>2023</v>
+        <v>2020</v>
       </c>
     </row>
     <row r="212" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A212">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B212" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="C212" t="s">
         <v>13</v>
@@ -6329,7 +6329,7 @@
         <v>18</v>
       </c>
       <c r="F212">
-        <v>2020</v>
+        <v>2023</v>
       </c>
     </row>
     <row r="213" spans="1:6" x14ac:dyDescent="0.35">
@@ -6337,7 +6337,7 @@
         <v>1</v>
       </c>
       <c r="B213" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="C213" t="s">
         <v>13</v>
@@ -6349,18 +6349,18 @@
         <v>18</v>
       </c>
       <c r="F213">
-        <v>2025</v>
+        <v>2020</v>
       </c>
     </row>
     <row r="214" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A214">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B214" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="C214" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D214" t="s">
         <v>261</v>
@@ -6369,38 +6369,38 @@
         <v>18</v>
       </c>
       <c r="F214">
-        <v>2019</v>
+        <v>2025</v>
       </c>
     </row>
     <row r="215" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A215">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B215" t="s">
+        <v>267</v>
+      </c>
+      <c r="C215" t="s">
+        <v>14</v>
+      </c>
+      <c r="D215" t="s">
+        <v>261</v>
+      </c>
+      <c r="E215" t="s">
+        <v>18</v>
+      </c>
+      <c r="F215">
+        <v>2019</v>
+      </c>
+    </row>
+    <row r="216" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A216">
+        <v>1</v>
+      </c>
+      <c r="B216" t="s">
         <v>268</v>
       </c>
-      <c r="C215" t="s">
+      <c r="C216" t="s">
         <v>7</v>
-      </c>
-      <c r="D215" t="s">
-        <v>269</v>
-      </c>
-      <c r="E215" t="s">
-        <v>24</v>
-      </c>
-      <c r="F215">
-        <v>2024</v>
-      </c>
-    </row>
-    <row r="216" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A216" t="s">
-        <v>27</v>
-      </c>
-      <c r="B216" t="s">
-        <v>270</v>
-      </c>
-      <c r="C216" t="s">
-        <v>12</v>
       </c>
       <c r="D216" t="s">
         <v>269</v>
@@ -6409,15 +6409,15 @@
         <v>24</v>
       </c>
       <c r="F216">
-        <v>2023</v>
+        <v>2024</v>
       </c>
     </row>
     <row r="217" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A217">
-        <v>2</v>
+      <c r="A217" t="s">
+        <v>27</v>
       </c>
       <c r="B217" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="C217" t="s">
         <v>12</v>
@@ -6429,18 +6429,18 @@
         <v>24</v>
       </c>
       <c r="F217">
-        <v>2022</v>
+        <v>2023</v>
       </c>
     </row>
     <row r="218" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A218" t="s">
-        <v>27</v>
+      <c r="A218">
+        <v>2</v>
       </c>
       <c r="B218" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="C218" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D218" t="s">
         <v>269</v>
@@ -6453,11 +6453,11 @@
       </c>
     </row>
     <row r="219" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A219">
-        <v>1</v>
+      <c r="A219" t="s">
+        <v>27</v>
       </c>
       <c r="B219" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="C219" t="s">
         <v>13</v>
@@ -6477,7 +6477,7 @@
         <v>1</v>
       </c>
       <c r="B220" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="C220" t="s">
         <v>13</v>
@@ -6489,18 +6489,18 @@
         <v>24</v>
       </c>
       <c r="F220">
-        <v>2026</v>
+        <v>2022</v>
       </c>
     </row>
     <row r="221" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A221">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B221" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="C221" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D221" t="s">
         <v>269</v>
@@ -6509,15 +6509,15 @@
         <v>24</v>
       </c>
       <c r="F221">
-        <v>2021</v>
+        <v>2026</v>
       </c>
     </row>
     <row r="222" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A222">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B222" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="C222" t="s">
         <v>14</v>
@@ -6529,27 +6529,27 @@
         <v>24</v>
       </c>
       <c r="F222">
-        <v>2016</v>
+        <v>2021</v>
       </c>
     </row>
     <row r="223" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A223" t="s">
-        <v>54</v>
+      <c r="A223">
+        <v>1</v>
       </c>
       <c r="B223" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="C223" t="s">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="D223" t="s">
-        <v>278</v>
+        <v>269</v>
       </c>
       <c r="E223" t="s">
         <v>24</v>
       </c>
       <c r="F223">
-        <v>2023</v>
+        <v>2016</v>
       </c>
     </row>
     <row r="224" spans="1:6" x14ac:dyDescent="0.35">
@@ -6557,10 +6557,10 @@
         <v>54</v>
       </c>
       <c r="B224" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="C224" t="s">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="D224" t="s">
         <v>278</v>
@@ -6569,18 +6569,18 @@
         <v>24</v>
       </c>
       <c r="F224">
-        <v>2021</v>
+        <v>2023</v>
       </c>
     </row>
     <row r="225" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A225" t="s">
-        <v>27</v>
+        <v>54</v>
       </c>
       <c r="B225" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="C225" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D225" t="s">
         <v>278</v>
@@ -6589,15 +6589,15 @@
         <v>24</v>
       </c>
       <c r="F225">
-        <v>2025</v>
+        <v>2021</v>
       </c>
     </row>
     <row r="226" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A226">
-        <v>1</v>
+      <c r="A226" t="s">
+        <v>27</v>
       </c>
       <c r="B226" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="C226" t="s">
         <v>13</v>
@@ -6609,15 +6609,15 @@
         <v>24</v>
       </c>
       <c r="F226">
-        <v>2023</v>
+        <v>2025</v>
       </c>
     </row>
     <row r="227" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A227" t="s">
-        <v>54</v>
+      <c r="A227">
+        <v>1</v>
       </c>
       <c r="B227" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="C227" t="s">
         <v>13</v>
@@ -6629,15 +6629,15 @@
         <v>24</v>
       </c>
       <c r="F227">
-        <v>2024</v>
+        <v>2023</v>
       </c>
     </row>
     <row r="228" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A228">
-        <v>1</v>
+      <c r="A228" t="s">
+        <v>54</v>
       </c>
       <c r="B228" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="C228" t="s">
         <v>13</v>
@@ -6649,7 +6649,7 @@
         <v>24</v>
       </c>
       <c r="F228">
-        <v>2022</v>
+        <v>2024</v>
       </c>
     </row>
     <row r="229" spans="1:6" x14ac:dyDescent="0.35">
@@ -6657,10 +6657,10 @@
         <v>1</v>
       </c>
       <c r="B229" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="C229" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D229" t="s">
         <v>278</v>
@@ -6669,15 +6669,15 @@
         <v>24</v>
       </c>
       <c r="F229">
-        <v>2021</v>
+        <v>2022</v>
       </c>
     </row>
     <row r="230" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A230">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B230" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="C230" t="s">
         <v>14</v>
@@ -6689,15 +6689,15 @@
         <v>24</v>
       </c>
       <c r="F230">
-        <v>2015</v>
+        <v>2021</v>
       </c>
     </row>
     <row r="231" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A231">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B231" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="C231" t="s">
         <v>14</v>
@@ -6709,21 +6709,21 @@
         <v>24</v>
       </c>
       <c r="F231">
-        <v>2025</v>
+        <v>2015</v>
       </c>
     </row>
     <row r="232" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A232" t="s">
-        <v>54</v>
+      <c r="A232">
+        <v>1</v>
       </c>
       <c r="B232" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="C232" t="s">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="D232" t="s">
-        <v>23</v>
+        <v>278</v>
       </c>
       <c r="E232" t="s">
         <v>24</v>
@@ -6733,14 +6733,14 @@
       </c>
     </row>
     <row r="233" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A233">
-        <v>2</v>
+      <c r="A233" t="s">
+        <v>54</v>
       </c>
       <c r="B233" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="C233" t="s">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="D233" t="s">
         <v>23</v>
@@ -6749,15 +6749,15 @@
         <v>24</v>
       </c>
       <c r="F233">
-        <v>2017</v>
+        <v>2025</v>
       </c>
     </row>
     <row r="234" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A234">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B234" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="C234" t="s">
         <v>12</v>
@@ -6769,7 +6769,7 @@
         <v>24</v>
       </c>
       <c r="F234">
-        <v>2023</v>
+        <v>2017</v>
       </c>
     </row>
     <row r="235" spans="1:6" x14ac:dyDescent="0.35">
@@ -6777,7 +6777,7 @@
         <v>1</v>
       </c>
       <c r="B235" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="C235" t="s">
         <v>12</v>
@@ -6789,18 +6789,18 @@
         <v>24</v>
       </c>
       <c r="F235">
-        <v>2026</v>
+        <v>2023</v>
       </c>
     </row>
     <row r="236" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A236" t="s">
-        <v>27</v>
+      <c r="A236">
+        <v>1</v>
       </c>
       <c r="B236" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="C236" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D236" t="s">
         <v>23</v>
@@ -6809,15 +6809,15 @@
         <v>24</v>
       </c>
       <c r="F236">
-        <v>2022</v>
+        <v>2026</v>
       </c>
     </row>
     <row r="237" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A237">
-        <v>1</v>
+      <c r="A237" t="s">
+        <v>27</v>
       </c>
       <c r="B237" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="C237" t="s">
         <v>13</v>
@@ -6829,15 +6829,15 @@
         <v>24</v>
       </c>
       <c r="F237">
-        <v>2026</v>
+        <v>2022</v>
       </c>
     </row>
     <row r="238" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A238">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B238" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="C238" t="s">
         <v>13</v>
@@ -6849,18 +6849,18 @@
         <v>24</v>
       </c>
       <c r="F238">
-        <v>2024</v>
+        <v>2026</v>
       </c>
     </row>
     <row r="239" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A239" t="s">
-        <v>54</v>
+      <c r="A239">
+        <v>2</v>
       </c>
       <c r="B239" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="C239" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D239" t="s">
         <v>23</v>
@@ -6869,15 +6869,15 @@
         <v>24</v>
       </c>
       <c r="F239">
-        <v>2020</v>
+        <v>2024</v>
       </c>
     </row>
     <row r="240" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A240">
-        <v>1</v>
+      <c r="A240" t="s">
+        <v>54</v>
       </c>
       <c r="B240" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="C240" t="s">
         <v>14</v>
@@ -6889,7 +6889,7 @@
         <v>24</v>
       </c>
       <c r="F240">
-        <v>2019</v>
+        <v>2020</v>
       </c>
     </row>
     <row r="241" spans="1:6" x14ac:dyDescent="0.35">
@@ -6897,30 +6897,30 @@
         <v>1</v>
       </c>
       <c r="B241" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="C241" t="s">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="D241" t="s">
-        <v>297</v>
+        <v>23</v>
       </c>
       <c r="E241" t="s">
         <v>24</v>
       </c>
       <c r="F241">
-        <v>2026</v>
+        <v>2019</v>
       </c>
     </row>
     <row r="242" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A242" t="s">
-        <v>54</v>
+      <c r="A242">
+        <v>1</v>
       </c>
       <c r="B242" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="C242" t="s">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="D242" t="s">
         <v>297</v>
@@ -6929,15 +6929,15 @@
         <v>24</v>
       </c>
       <c r="F242">
-        <v>2024</v>
+        <v>2026</v>
       </c>
     </row>
     <row r="243" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A243">
-        <v>1</v>
+      <c r="A243" t="s">
+        <v>54</v>
       </c>
       <c r="B243" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="C243" t="s">
         <v>12</v>
@@ -6949,7 +6949,7 @@
         <v>24</v>
       </c>
       <c r="F243">
-        <v>2021</v>
+        <v>2024</v>
       </c>
     </row>
     <row r="244" spans="1:6" x14ac:dyDescent="0.35">
@@ -6957,7 +6957,7 @@
         <v>1</v>
       </c>
       <c r="B244" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="C244" t="s">
         <v>12</v>
@@ -6969,7 +6969,7 @@
         <v>24</v>
       </c>
       <c r="F244">
-        <v>2023</v>
+        <v>2021</v>
       </c>
     </row>
     <row r="245" spans="1:6" x14ac:dyDescent="0.35">
@@ -6977,10 +6977,10 @@
         <v>1</v>
       </c>
       <c r="B245" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="C245" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D245" t="s">
         <v>297</v>
@@ -6989,15 +6989,15 @@
         <v>24</v>
       </c>
       <c r="F245">
-        <v>2026</v>
+        <v>2023</v>
       </c>
     </row>
     <row r="246" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A246" t="s">
-        <v>54</v>
+      <c r="A246">
+        <v>1</v>
       </c>
       <c r="B246" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="C246" t="s">
         <v>13</v>
@@ -7009,7 +7009,7 @@
         <v>24</v>
       </c>
       <c r="F246">
-        <v>2025</v>
+        <v>2026</v>
       </c>
     </row>
     <row r="247" spans="1:6" x14ac:dyDescent="0.35">
@@ -7017,7 +7017,7 @@
         <v>54</v>
       </c>
       <c r="B247" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="C247" t="s">
         <v>13</v>
@@ -7029,15 +7029,15 @@
         <v>24</v>
       </c>
       <c r="F247">
-        <v>2017</v>
+        <v>2025</v>
       </c>
     </row>
     <row r="248" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A248">
-        <v>1</v>
+      <c r="A248" t="s">
+        <v>54</v>
       </c>
       <c r="B248" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="C248" t="s">
         <v>13</v>
@@ -7049,18 +7049,18 @@
         <v>24</v>
       </c>
       <c r="F248">
-        <v>2025</v>
+        <v>2017</v>
       </c>
     </row>
     <row r="249" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A249">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B249" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="C249" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D249" t="s">
         <v>297</v>
@@ -7069,38 +7069,38 @@
         <v>24</v>
       </c>
       <c r="F249">
-        <v>2022</v>
+        <v>2025</v>
       </c>
     </row>
     <row r="250" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A250">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B250" t="s">
+        <v>305</v>
+      </c>
+      <c r="C250" t="s">
+        <v>14</v>
+      </c>
+      <c r="D250" t="s">
+        <v>297</v>
+      </c>
+      <c r="E250" t="s">
+        <v>24</v>
+      </c>
+      <c r="F250">
+        <v>2022</v>
+      </c>
+    </row>
+    <row r="251" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A251">
+        <v>1</v>
+      </c>
+      <c r="B251" t="s">
         <v>306</v>
       </c>
-      <c r="C250" t="s">
+      <c r="C251" t="s">
         <v>7</v>
-      </c>
-      <c r="D250" t="s">
-        <v>307</v>
-      </c>
-      <c r="E250" t="s">
-        <v>19</v>
-      </c>
-      <c r="F250">
-        <v>2016</v>
-      </c>
-    </row>
-    <row r="251" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A251" t="s">
-        <v>54</v>
-      </c>
-      <c r="B251" t="s">
-        <v>308</v>
-      </c>
-      <c r="C251" t="s">
-        <v>12</v>
       </c>
       <c r="D251" t="s">
         <v>307</v>
@@ -7109,15 +7109,15 @@
         <v>19</v>
       </c>
       <c r="F251">
-        <v>2026</v>
+        <v>2016</v>
       </c>
     </row>
     <row r="252" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A252">
-        <v>2</v>
+      <c r="A252" t="s">
+        <v>54</v>
       </c>
       <c r="B252" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="C252" t="s">
         <v>12</v>
@@ -7129,7 +7129,7 @@
         <v>19</v>
       </c>
       <c r="F252">
-        <v>2022</v>
+        <v>2026</v>
       </c>
     </row>
     <row r="253" spans="1:6" x14ac:dyDescent="0.35">
@@ -7137,10 +7137,10 @@
         <v>2</v>
       </c>
       <c r="B253" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="C253" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D253" t="s">
         <v>307</v>
@@ -7149,7 +7149,7 @@
         <v>19</v>
       </c>
       <c r="F253">
-        <v>2024</v>
+        <v>2022</v>
       </c>
     </row>
     <row r="254" spans="1:6" x14ac:dyDescent="0.35">
